--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>掉落id</t>
   </si>
@@ -51,7 +51,7 @@
     <t>雇员</t>
   </si>
   <si>
-    <t>550_1026001_1|550_1026002_1|550_1027001_1|550_1027002_1|550_1028001_1|550_1028002_1|300_1026101_1|300_1026102_1|300_1027101_1|300_1027102_1|300_1028101_1|300_1028102_1|100_1026201_1|100_1026202_1|100_1027201_1|100_1027202_1|100_1028201_1|100_1028202_1|40_1026301_1|40_1026302_1|40_1027301_1|40_1027302_1|40_1028301_1|40_1028302_1|15_1026401_1|15_1026402_1|15_1027401_1|15_1027402_1|15_1028401_1|15_1028402_1</t>
+    <t>550_1026001_1|550_1027001_1|550_1028001_1|300_1026101_1|300_1027101_1|300_1028101_1|100_1026201_1|100_1027201_1|100_1028201_1|40_1026301_1|40_1027301_1|40_1028301_1|15_1026401_1|15_1027401_1|15_1028401_1</t>
   </si>
   <si>
     <t>权重1</t>
@@ -1301,16 +1301,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:K43"/>
+  <dimension ref="A2:M43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="4" spans="1:11">
+    <row r="2" spans="1:13">
+      <c r="J2" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,M7:M42)</f>
+        <v>550_1026001_1|550_1027001_1|550_1028001_1|300_1026101_1|300_1027101_1|300_1028101_1|100_1026201_1|100_1027201_1|100_1028201_1|40_1026301_1|40_1027301_1|40_1028301_1|15_1026401_1|15_1027401_1|15_1028401_1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="J4" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,J7:J43)</f>
         <v>600_1026001_1|600_1026002_1|600_1027001_1|600_1027002_1|600_1028001_1|600_1028002_1|350_1026201_1|350_1026202_1|350_1027201_1|350_1027202_1|350_1028201_1|350_1028202_1|50_1026401_1|50_1026402_1|50_1027401_1|50_1027402_1|50_1028401_1|50_1028402_1</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -1328,7 +1334,7 @@
         <v>550_1026001_1|550_1026002_1|550_1027001_1|550_1027002_1|550_1028001_1|550_1028002_1|300_1026101_1|300_1026102_1|300_1027101_1|300_1027102_1|300_1028101_1|300_1028102_1|100_1026201_1|100_1026202_1|100_1027201_1|100_1027202_1|100_1028201_1|100_1028202_1|40_1026301_1|40_1026302_1|40_1027301_1|40_1027302_1|40_1028301_1|40_1028302_1|15_1026401_1|15_1026402_1|15_1027401_1|15_1027402_1|15_1028401_1|15_1028402_1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="C7">
         <v>600</v>
       </c>
@@ -1336,6 +1342,9 @@
         <v>550</v>
       </c>
       <c r="E7" s="1">
+        <v>1026001</v>
+      </c>
+      <c r="F7" s="1">
         <v>1026001</v>
       </c>
       <c r="G7">
@@ -1349,8 +1358,12 @@
         <f t="shared" ref="K7:K15" si="1">_xlfn.TEXTJOIN("_",TRUE,D7,E7,G7)</f>
         <v>550_1026001_1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D7,F7,G7)</f>
+        <v>550_1026001_1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="C8">
         <v>600</v>
       </c>
@@ -1360,6 +1373,7 @@
       <c r="E8" s="1">
         <v>1026002</v>
       </c>
+      <c r="F8" s="1"/>
       <c r="G8">
         <v>1</v>
       </c>
@@ -1372,7 +1386,7 @@
         <v>550_1026002_1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="C9">
         <v>600</v>
       </c>
@@ -1380,6 +1394,9 @@
         <v>550</v>
       </c>
       <c r="E9" s="1">
+        <v>1027001</v>
+      </c>
+      <c r="F9" s="1">
         <v>1027001</v>
       </c>
       <c r="G9">
@@ -1393,8 +1410,12 @@
         <f t="shared" si="1"/>
         <v>550_1027001_1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D9,F9,G9)</f>
+        <v>550_1027001_1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1407,6 +1428,7 @@
       <c r="E10" s="1">
         <v>1027002</v>
       </c>
+      <c r="F10" s="1"/>
       <c r="G10">
         <v>1</v>
       </c>
@@ -1419,7 +1441,7 @@
         <v>550_1027002_1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>1026001</v>
       </c>
@@ -1430,6 +1452,9 @@
         <v>550</v>
       </c>
       <c r="E11" s="1">
+        <v>1028001</v>
+      </c>
+      <c r="F11" s="1">
         <v>1028001</v>
       </c>
       <c r="G11">
@@ -1443,8 +1468,12 @@
         <f t="shared" si="1"/>
         <v>550_1028001_1</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M11" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D11,F11,G11)</f>
+        <v>550_1028001_1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>1026002</v>
       </c>
@@ -1457,6 +1486,7 @@
       <c r="E12" s="1">
         <v>1028002</v>
       </c>
+      <c r="F12" s="1"/>
       <c r="G12">
         <v>1</v>
       </c>
@@ -1469,7 +1499,7 @@
         <v>550_1028002_1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>1026101</v>
       </c>
@@ -1481,8 +1511,12 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="M13" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D13,F13,G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>1026102</v>
       </c>
@@ -1494,8 +1528,12 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="M14" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D14,F14,G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>1026201</v>
       </c>
@@ -1507,16 +1545,23 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="M15" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D15,F15,G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>1026202</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>1026301</v>
       </c>
@@ -1524,6 +1569,9 @@
         <v>300</v>
       </c>
       <c r="E17" s="1">
+        <v>1026101</v>
+      </c>
+      <c r="F17" s="1">
         <v>1026101</v>
       </c>
       <c r="G17">
@@ -1533,8 +1581,12 @@
         <f t="shared" ref="K17:K22" si="2">_xlfn.TEXTJOIN("_",TRUE,D17,E17,G17)</f>
         <v>300_1026101_1</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="M17" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D17,F17,G17)</f>
+        <v>300_1026101_1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>1026302</v>
       </c>
@@ -1544,6 +1596,7 @@
       <c r="E18" s="1">
         <v>1026102</v>
       </c>
+      <c r="F18" s="1"/>
       <c r="G18">
         <v>1</v>
       </c>
@@ -1552,7 +1605,7 @@
         <v>300_1026102_1</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>1026401</v>
       </c>
@@ -1560,6 +1613,9 @@
         <v>300</v>
       </c>
       <c r="E19" s="1">
+        <v>1027101</v>
+      </c>
+      <c r="F19" s="1">
         <v>1027101</v>
       </c>
       <c r="G19">
@@ -1569,8 +1625,12 @@
         <f t="shared" si="2"/>
         <v>300_1027101_1</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="M19" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D19,F19,G19)</f>
+        <v>300_1027101_1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>1026402</v>
       </c>
@@ -1580,6 +1640,7 @@
       <c r="E20" s="1">
         <v>1027102</v>
       </c>
+      <c r="F20" s="1"/>
       <c r="G20">
         <v>1</v>
       </c>
@@ -1588,7 +1649,7 @@
         <v>300_1027102_1</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>1027001</v>
       </c>
@@ -1596,6 +1657,9 @@
         <v>300</v>
       </c>
       <c r="E21" s="1">
+        <v>1028101</v>
+      </c>
+      <c r="F21" s="1">
         <v>1028101</v>
       </c>
       <c r="G21">
@@ -1605,8 +1669,12 @@
         <f t="shared" si="2"/>
         <v>300_1028101_1</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="M21" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D21,F21,G21)</f>
+        <v>300_1028101_1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>1027002</v>
       </c>
@@ -1616,6 +1684,7 @@
       <c r="E22" s="1">
         <v>1028102</v>
       </c>
+      <c r="F22" s="1"/>
       <c r="G22">
         <v>1</v>
       </c>
@@ -1624,15 +1693,18 @@
         <v>300_1028102_1</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>1027101</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>1027102</v>
       </c>
@@ -1643,6 +1715,9 @@
         <v>100</v>
       </c>
       <c r="E24" s="1">
+        <v>1026201</v>
+      </c>
+      <c r="F24" s="1">
         <v>1026201</v>
       </c>
       <c r="G24">
@@ -1656,8 +1731,12 @@
         <f t="shared" ref="K24:K29" si="4">_xlfn.TEXTJOIN("_",TRUE,D24,E24,G24)</f>
         <v>100_1026201_1</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="M24" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D24,F24,G24)</f>
+        <v>100_1026201_1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>1027201</v>
       </c>
@@ -1670,6 +1749,7 @@
       <c r="E25" s="1">
         <v>1026202</v>
       </c>
+      <c r="F25" s="1"/>
       <c r="G25">
         <v>1</v>
       </c>
@@ -1682,7 +1762,7 @@
         <v>100_1026202_1</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>1027202</v>
       </c>
@@ -1693,6 +1773,9 @@
         <v>100</v>
       </c>
       <c r="E26" s="1">
+        <v>1027201</v>
+      </c>
+      <c r="F26" s="1">
         <v>1027201</v>
       </c>
       <c r="G26">
@@ -1706,8 +1789,12 @@
         <f t="shared" si="4"/>
         <v>100_1027201_1</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="M26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D26,F26,G26)</f>
+        <v>100_1027201_1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>1027301</v>
       </c>
@@ -1720,6 +1807,7 @@
       <c r="E27" s="1">
         <v>1027202</v>
       </c>
+      <c r="F27" s="1"/>
       <c r="G27">
         <v>1</v>
       </c>
@@ -1732,7 +1820,7 @@
         <v>100_1027202_1</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>1027302</v>
       </c>
@@ -1743,6 +1831,9 @@
         <v>100</v>
       </c>
       <c r="E28" s="1">
+        <v>1028201</v>
+      </c>
+      <c r="F28" s="1">
         <v>1028201</v>
       </c>
       <c r="G28">
@@ -1756,8 +1847,12 @@
         <f t="shared" si="4"/>
         <v>100_1028201_1</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="M28" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D28,F28,G28)</f>
+        <v>100_1028201_1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>1027401</v>
       </c>
@@ -1770,6 +1865,7 @@
       <c r="E29" s="1">
         <v>1028202</v>
       </c>
+      <c r="F29" s="1"/>
       <c r="G29">
         <v>1</v>
       </c>
@@ -1782,15 +1878,18 @@
         <v>100_1028202_1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>1027402</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>1028001</v>
       </c>
@@ -1798,6 +1897,9 @@
         <v>40</v>
       </c>
       <c r="E31" s="1">
+        <v>1026301</v>
+      </c>
+      <c r="F31" s="1">
         <v>1026301</v>
       </c>
       <c r="G31">
@@ -1807,8 +1909,12 @@
         <f t="shared" ref="K31:K36" si="5">_xlfn.TEXTJOIN("_",TRUE,D31,E31,G31)</f>
         <v>40_1026301_1</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="M31" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D31,F31,G31)</f>
+        <v>40_1026301_1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>1028002</v>
       </c>
@@ -1818,6 +1924,7 @@
       <c r="E32" s="1">
         <v>1026302</v>
       </c>
+      <c r="F32" s="1"/>
       <c r="G32">
         <v>1</v>
       </c>
@@ -1826,7 +1933,7 @@
         <v>40_1026302_1</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>1028101</v>
       </c>
@@ -1834,6 +1941,9 @@
         <v>40</v>
       </c>
       <c r="E33" s="1">
+        <v>1027301</v>
+      </c>
+      <c r="F33" s="1">
         <v>1027301</v>
       </c>
       <c r="G33">
@@ -1843,8 +1953,12 @@
         <f t="shared" si="5"/>
         <v>40_1027301_1</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="M33" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D33,F33,G33)</f>
+        <v>40_1027301_1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>1028102</v>
       </c>
@@ -1854,6 +1968,7 @@
       <c r="E34" s="1">
         <v>1027302</v>
       </c>
+      <c r="F34" s="1"/>
       <c r="G34">
         <v>1</v>
       </c>
@@ -1862,7 +1977,7 @@
         <v>40_1027302_1</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>1028201</v>
       </c>
@@ -1870,6 +1985,9 @@
         <v>40</v>
       </c>
       <c r="E35" s="1">
+        <v>1028301</v>
+      </c>
+      <c r="F35" s="1">
         <v>1028301</v>
       </c>
       <c r="G35">
@@ -1879,8 +1997,12 @@
         <f t="shared" si="5"/>
         <v>40_1028301_1</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="M35" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D35,F35,G35)</f>
+        <v>40_1028301_1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>1028202</v>
       </c>
@@ -1890,6 +2012,7 @@
       <c r="E36" s="1">
         <v>1028302</v>
       </c>
+      <c r="F36" s="1"/>
       <c r="G36">
         <v>1</v>
       </c>
@@ -1898,15 +2021,18 @@
         <v>40_1028302_1</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>1028301</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>1028302</v>
       </c>
@@ -1917,6 +2043,9 @@
         <v>15</v>
       </c>
       <c r="E38" s="1">
+        <v>1026401</v>
+      </c>
+      <c r="F38" s="1">
         <v>1026401</v>
       </c>
       <c r="G38">
@@ -1930,8 +2059,12 @@
         <f t="shared" ref="K38:K43" si="7">_xlfn.TEXTJOIN("_",TRUE,D38,E38,G38)</f>
         <v>15_1026401_1</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="M38" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D38,F38,G38)</f>
+        <v>15_1026401_1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>1028401</v>
       </c>
@@ -1944,6 +2077,7 @@
       <c r="E39" s="1">
         <v>1026402</v>
       </c>
+      <c r="F39" s="1"/>
       <c r="G39">
         <v>1</v>
       </c>
@@ -1956,7 +2090,7 @@
         <v>15_1026402_1</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>1028402</v>
       </c>
@@ -1967,6 +2101,9 @@
         <v>15</v>
       </c>
       <c r="E40" s="1">
+        <v>1027401</v>
+      </c>
+      <c r="F40" s="1">
         <v>1027401</v>
       </c>
       <c r="G40">
@@ -1980,8 +2117,12 @@
         <f t="shared" si="7"/>
         <v>15_1027401_1</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="M40" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D40,F40,G40)</f>
+        <v>15_1027401_1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="C41">
         <v>50</v>
       </c>
@@ -1991,6 +2132,7 @@
       <c r="E41" s="1">
         <v>1027402</v>
       </c>
+      <c r="F41" s="1"/>
       <c r="G41">
         <v>1</v>
       </c>
@@ -2003,7 +2145,7 @@
         <v>15_1027402_1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:13">
       <c r="C42">
         <v>50</v>
       </c>
@@ -2011,6 +2153,9 @@
         <v>15</v>
       </c>
       <c r="E42" s="1">
+        <v>1028401</v>
+      </c>
+      <c r="F42" s="1">
         <v>1028401</v>
       </c>
       <c r="G42">
@@ -2024,8 +2169,12 @@
         <f t="shared" si="7"/>
         <v>15_1028401_1</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="M42" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D42,F42,G42)</f>
+        <v>15_1028401_1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="C43">
         <v>50</v>
       </c>
@@ -2035,6 +2184,7 @@
       <c r="E43" s="1">
         <v>1028402</v>
       </c>
+      <c r="F43" s="1"/>
       <c r="G43">
         <v>1</v>
       </c>

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -51,7 +51,7 @@
     <t>雇员</t>
   </si>
   <si>
-    <t>550_1026001_1|550_1027001_1|550_1028001_1|300_1026101_1|300_1027101_1|300_1028101_1|100_1026201_1|100_1027201_1|100_1028201_1|40_1026301_1|40_1027301_1|40_1028301_1|15_1026401_1|15_1027401_1|15_1028401_1</t>
+    <t>550_1026001_1|550_1026002_1|550_1027001_1|550_1027002_1|550_1028001_1|550_1028002_1|300_1026101_1|300_1026102_1|300_1027101_1|300_1027102_1|300_1028101_1|300_1028102_1|100_1026201_1|100_1026202_1|100_1027201_1|100_1027202_1|100_1028201_1|100_1028202_1|40_1026301_1|40_1026302_1|40_1027301_1|40_1027302_1|40_1028301_1|40_1028302_1|15_1026401_1|15_1026402_1|15_1027401_1|15_1027402_1|15_1028401_1|15_1028402_1</t>
   </si>
   <si>
     <t>权重1</t>

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -28,9 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>掉落id</t>
+  </si>
+  <si>
+    <t>新手引导抽奖</t>
   </si>
   <si>
     <t>权重_道具ID_数量</t>
@@ -43,6 +46,9 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>NewbieGuideDraw</t>
   </si>
   <si>
     <t>detailedDropItem</t>
@@ -1241,10 +1247,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:3">
+    <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1252,45 +1261,59 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:3">
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:3">
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:3">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="2">
         <v>2001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1026001</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1318,16 +1341,16 @@
     </row>
     <row r="5" spans="1:13">
       <c r="C5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,K7:K43)</f>
@@ -1417,7 +1440,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>600</v>
@@ -1555,10 +1578,10 @@
         <v>1026202</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1698,10 +1721,10 @@
         <v>1027101</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1883,10 +1906,10 @@
         <v>1027402</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2026,10 +2049,10 @@
         <v>1028301</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:13">

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -28,12 +28,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>掉落id</t>
   </si>
   <si>
     <t>新手引导抽奖</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>权重_道具ID_数量</t>
@@ -55,6 +58,9 @@
   </si>
   <si>
     <t>雇员</t>
+  </si>
+  <si>
+    <t>亨利</t>
   </si>
   <si>
     <t>550_1026001_1|550_1026002_1|550_1027001_1|550_1027002_1|550_1028001_1|550_1028002_1|300_1026101_1|300_1026102_1|300_1027101_1|300_1027102_1|300_1028101_1|300_1028102_1|100_1026201_1|100_1026202_1|100_1027201_1|100_1027202_1|100_1028201_1|100_1028202_1|40_1026301_1|40_1026302_1|40_1027301_1|40_1027302_1|40_1028301_1|40_1028302_1|15_1026401_1|15_1026402_1|15_1027401_1|15_1027402_1|15_1028401_1|15_1028402_1</t>
@@ -1247,13 +1253,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1264,56 +1270,66 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:4">
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:4">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:4">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:4">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2">
         <v>2001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2">
-        <v>1026001</v>
+        <v>1026101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:4">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1341,16 +1357,16 @@
     </row>
     <row r="5" spans="1:13">
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,K7:K43)</f>
@@ -1440,7 +1456,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>600</v>
@@ -1578,10 +1594,10 @@
         <v>1026202</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1721,10 +1737,10 @@
         <v>1027101</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1906,10 +1922,10 @@
         <v>1027402</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2049,10 +2065,10 @@
         <v>1028301</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:13">

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeePool" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+道具ID_引导ID1_引导ID2_引导ID3
+注：引导时，雇员抽卡 出指定 雇员。 引导ID判断有一个匹配 就出这个字段中的雇员
+引导ID:可以配置多个 避免抽卡步骤与服务器校验的不准确</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>掉落id</t>
   </si>
@@ -45,6 +79,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
@@ -58,6 +95,9 @@
   </si>
   <si>
     <t>雇员</t>
+  </si>
+  <si>
+    <t>1026101_1844_1845_1846</t>
   </si>
   <si>
     <t>亨利</t>
@@ -103,7 +143,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +306,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -718,7 +769,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -727,6 +778,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1256,7 +1310,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1280,24 +1334,24 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
@@ -1312,16 +1366,16 @@
         <v>2001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1026101</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:5">
@@ -1334,6 +1388,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1357,16 +1412,16 @@
     </row>
     <row r="5" spans="1:13">
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,K7:K43)</f>
@@ -1456,7 +1511,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>600</v>
@@ -1594,10 +1649,10 @@
         <v>1026202</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1737,10 +1792,10 @@
         <v>1027101</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1922,10 +1977,10 @@
         <v>1027402</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2065,10 +2120,10 @@
         <v>1028301</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:13">

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -97,7 +102,7 @@
     <t>雇员</t>
   </si>
   <si>
-    <t>1026101_1844_1845_1846</t>
+    <t>1026101_1604_1605_1606_1607</t>
   </si>
   <si>
     <t>亨利</t>
@@ -1310,7 +1315,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="27.125" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -102,7 +102,7 @@
     <t>雇员</t>
   </si>
   <si>
-    <t>1026101_1604_1605_1606_1607</t>
+    <t>1026101_1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
   </si>
   <si>
     <t>亨利</t>
@@ -1315,7 +1315,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="3" max="3" width="74.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">

--- a/hall/resources/sample/EmployeePool.xlsx
+++ b/hall/resources/sample/EmployeePool.xlsx
@@ -102,7 +102,7 @@
     <t>雇员</t>
   </si>
   <si>
-    <t>1026101_1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
+    <t>1026101_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
   </si>
   <si>
     <t>亨利</t>
